--- a/PantryWiseApp/tests/PantryWise_Appium_TestCases.xlsx
+++ b/PantryWiseApp/tests/PantryWise_Appium_TestCases.xlsx
@@ -15140,7 +15140,7 @@
         <v>Generated On</v>
       </c>
       <c r="B3" t="str">
-        <v>26/7/2026, 3:48:16 pm</v>
+        <v>26/7/2026, 4:41:33 pm</v>
       </c>
     </row>
     <row r="4">
